--- a/database/db/thirds_departments.xlsx
+++ b/database/db/thirds_departments.xlsx
@@ -3180,7 +3180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:C1892"/>
+  <dimension ref="A1:C1791"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
@@ -22886,309 +22886,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1792" spans="1:1">
-      <c r="A1792"/>
-    </row>
-    <row r="1793" spans="1:1">
-      <c r="A1793"/>
-    </row>
-    <row r="1794" spans="1:1">
-      <c r="A1794"/>
-    </row>
-    <row r="1795" spans="1:1">
-      <c r="A1795"/>
-    </row>
-    <row r="1796" spans="1:1">
-      <c r="A1796"/>
-    </row>
-    <row r="1797" spans="1:1">
-      <c r="A1797"/>
-    </row>
-    <row r="1798" spans="1:1">
-      <c r="A1798"/>
-    </row>
-    <row r="1799" spans="1:1">
-      <c r="A1799"/>
-    </row>
-    <row r="1800" spans="1:1">
-      <c r="A1800"/>
-    </row>
-    <row r="1801" spans="1:1">
-      <c r="A1801"/>
-    </row>
-    <row r="1802" spans="1:1">
-      <c r="A1802"/>
-    </row>
-    <row r="1803" spans="1:1">
-      <c r="A1803"/>
-    </row>
-    <row r="1804" spans="1:1">
-      <c r="A1804"/>
-    </row>
-    <row r="1805" spans="1:1">
-      <c r="A1805"/>
-    </row>
-    <row r="1806" spans="1:1">
-      <c r="A1806"/>
-    </row>
-    <row r="1807" spans="1:1">
-      <c r="A1807"/>
-    </row>
-    <row r="1808" spans="1:1">
-      <c r="A1808"/>
-    </row>
-    <row r="1809" spans="1:1">
-      <c r="A1809"/>
-    </row>
-    <row r="1810" spans="1:1">
-      <c r="A1810"/>
-    </row>
-    <row r="1811" spans="1:1">
-      <c r="A1811"/>
-    </row>
-    <row r="1812" spans="1:1">
-      <c r="A1812"/>
-    </row>
-    <row r="1813" spans="1:1">
-      <c r="A1813"/>
-    </row>
-    <row r="1814" spans="1:1">
-      <c r="A1814"/>
-    </row>
-    <row r="1815" spans="1:1">
-      <c r="A1815"/>
-    </row>
-    <row r="1816" spans="1:1">
-      <c r="A1816"/>
-    </row>
-    <row r="1817" spans="1:1">
-      <c r="A1817"/>
-    </row>
-    <row r="1818" spans="1:1">
-      <c r="A1818"/>
-    </row>
-    <row r="1819" spans="1:1">
-      <c r="A1819"/>
-    </row>
-    <row r="1820" spans="1:1">
-      <c r="A1820"/>
-    </row>
-    <row r="1821" spans="1:1">
-      <c r="A1821"/>
-    </row>
-    <row r="1822" spans="1:1">
-      <c r="A1822"/>
-    </row>
-    <row r="1823" spans="1:1">
-      <c r="A1823"/>
-    </row>
-    <row r="1824" spans="1:1">
-      <c r="A1824"/>
-    </row>
-    <row r="1825" spans="1:1">
-      <c r="A1825"/>
-    </row>
-    <row r="1826" spans="1:1">
-      <c r="A1826"/>
-    </row>
-    <row r="1827" spans="1:1">
-      <c r="A1827"/>
-    </row>
-    <row r="1828" spans="1:1">
-      <c r="A1828"/>
-    </row>
-    <row r="1829" spans="1:1">
-      <c r="A1829"/>
-    </row>
-    <row r="1830" spans="1:1">
-      <c r="A1830"/>
-    </row>
-    <row r="1831" spans="1:1">
-      <c r="A1831"/>
-    </row>
-    <row r="1832" spans="1:1">
-      <c r="A1832"/>
-    </row>
-    <row r="1833" spans="1:1">
-      <c r="A1833"/>
-    </row>
-    <row r="1834" spans="1:1">
-      <c r="A1834"/>
-    </row>
-    <row r="1835" spans="1:1">
-      <c r="A1835"/>
-    </row>
-    <row r="1836" spans="1:1">
-      <c r="A1836"/>
-    </row>
-    <row r="1837" spans="1:1">
-      <c r="A1837"/>
-    </row>
-    <row r="1838" spans="1:1">
-      <c r="A1838"/>
-    </row>
-    <row r="1839" spans="1:1">
-      <c r="A1839"/>
-    </row>
-    <row r="1840" spans="1:1">
-      <c r="A1840"/>
-    </row>
-    <row r="1841" spans="1:1">
-      <c r="A1841"/>
-    </row>
-    <row r="1842" spans="1:1">
-      <c r="A1842"/>
-    </row>
-    <row r="1843" spans="1:1">
-      <c r="A1843"/>
-    </row>
-    <row r="1844" spans="1:1">
-      <c r="A1844"/>
-    </row>
-    <row r="1845" spans="1:1">
-      <c r="A1845"/>
-    </row>
-    <row r="1846" spans="1:1">
-      <c r="A1846"/>
-    </row>
-    <row r="1847" spans="1:1">
-      <c r="A1847"/>
-    </row>
-    <row r="1848" spans="1:1">
-      <c r="A1848"/>
-    </row>
-    <row r="1849" spans="1:1">
-      <c r="A1849"/>
-    </row>
-    <row r="1850" spans="1:1">
-      <c r="A1850"/>
-    </row>
-    <row r="1851" spans="1:1">
-      <c r="A1851"/>
-    </row>
-    <row r="1852" spans="1:1">
-      <c r="A1852"/>
-    </row>
-    <row r="1853" spans="1:1">
-      <c r="A1853"/>
-    </row>
-    <row r="1854" spans="1:1">
-      <c r="A1854"/>
-    </row>
-    <row r="1855" spans="1:1">
-      <c r="A1855"/>
-    </row>
-    <row r="1856" spans="1:1">
-      <c r="A1856"/>
-    </row>
-    <row r="1857" spans="1:1">
-      <c r="A1857"/>
-    </row>
-    <row r="1858" spans="1:1">
-      <c r="A1858"/>
-    </row>
-    <row r="1859" spans="1:1">
-      <c r="A1859"/>
-    </row>
-    <row r="1860" spans="1:1">
-      <c r="A1860"/>
-    </row>
-    <row r="1861" spans="1:1">
-      <c r="A1861"/>
-    </row>
-    <row r="1862" spans="1:1">
-      <c r="A1862"/>
-    </row>
-    <row r="1863" spans="1:1">
-      <c r="A1863"/>
-    </row>
-    <row r="1864" spans="1:1">
-      <c r="A1864"/>
-    </row>
-    <row r="1865" spans="1:1">
-      <c r="A1865"/>
-    </row>
-    <row r="1866" spans="1:1">
-      <c r="A1866"/>
-    </row>
-    <row r="1867" spans="1:1">
-      <c r="A1867"/>
-    </row>
-    <row r="1868" spans="1:1">
-      <c r="A1868"/>
-    </row>
-    <row r="1869" spans="1:1">
-      <c r="A1869"/>
-    </row>
-    <row r="1870" spans="1:1">
-      <c r="A1870"/>
-    </row>
-    <row r="1871" spans="1:1">
-      <c r="A1871"/>
-    </row>
-    <row r="1872" spans="1:1">
-      <c r="A1872"/>
-    </row>
-    <row r="1873" spans="1:1">
-      <c r="A1873"/>
-    </row>
-    <row r="1874" spans="1:1">
-      <c r="A1874"/>
-    </row>
-    <row r="1875" spans="1:1">
-      <c r="A1875"/>
-    </row>
-    <row r="1876" spans="1:1">
-      <c r="A1876"/>
-    </row>
-    <row r="1877" spans="1:1">
-      <c r="A1877"/>
-    </row>
-    <row r="1878" spans="1:1">
-      <c r="A1878"/>
-    </row>
-    <row r="1879" spans="1:1">
-      <c r="A1879"/>
-    </row>
-    <row r="1880" spans="1:1">
-      <c r="A1880"/>
-    </row>
-    <row r="1881" spans="1:1">
-      <c r="A1881"/>
-    </row>
-    <row r="1882" spans="1:1">
-      <c r="A1882"/>
-    </row>
-    <row r="1883" spans="1:1">
-      <c r="A1883"/>
-    </row>
-    <row r="1884" spans="1:1">
-      <c r="A1884"/>
-    </row>
-    <row r="1885" spans="1:1">
-      <c r="A1885"/>
-    </row>
-    <row r="1886" spans="1:1">
-      <c r="A1886"/>
-    </row>
-    <row r="1887" spans="1:1">
-      <c r="A1887"/>
-    </row>
-    <row r="1888" spans="1:1">
-      <c r="A1888"/>
-    </row>
-    <row r="1889" spans="1:1">
-      <c r="A1889"/>
-    </row>
-    <row r="1890" spans="1:1">
-      <c r="A1890"/>
-    </row>
-    <row r="1891" spans="1:1">
-      <c r="A1891"/>
-    </row>
-    <row r="1892" spans="1:1">
-      <c r="A1892"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
